--- a/business_surveys/028_transparency_communication_practices_survey--business_surveys.xlsx
+++ b/business_surveys/028_transparency_communication_practices_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'2-1',_'name':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '2-1', 'name': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'2-2',_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '2-2', 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'2-3',_'name':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '2-3', 'name': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'3-1',_'name':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '3-1', 'name': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'3-2',_'name':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '3-2', 'name': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'3-3',_'name':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '3-3', 'name': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'4-1',_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '4-1', 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'4-2',_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '4-2', 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'4-3',_'name':_'video_calls'}</t>
+          <t>video_calls</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '4-3', 'name': 'Video calls'}</t>
+          <t>Video calls</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'4-4',_'name':_'text_messages'}</t>
+          <t>text_messages</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '4-4', 'name': 'Text messages'}</t>
+          <t>Text messages</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'5-1',_'name':_'colleagues'}</t>
+          <t>colleagues</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': '5-1', 'name': 'Colleagues'}</t>
+          <t>Colleagues</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'5-2',_'name':_'management'}</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': '5-2', 'name': 'Management'}</t>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'5-3',_'name':_'clients'}</t>
+          <t>clients</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': '5-3', 'name': 'Clients'}</t>
+          <t>Clients</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'5-4',_'name':_'suppliers'}</t>
+          <t>suppliers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': '5-4', 'name': 'Suppliers'}</t>
+          <t>Suppliers</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_'6-1',_'name':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': '6-1', 'name': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_'6-2',_'name':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': '6-2', 'name': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_'6-3',_'name':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': '6-3', 'name': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_'7-1',_'name':_'financial_information'}</t>
+          <t>financial_information</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': '7-1', 'name': 'Financial information'}</t>
+          <t>Financial information</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_'7-2',_'name':_'performance_information'}</t>
+          <t>performance_information</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': '7-2', 'name': 'Performance information'}</t>
+          <t>Performance information</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_'7-3',_'name':_'other_data'}</t>
+          <t>other_data</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': '7-3', 'name': 'Other data'}</t>
+          <t>Other data</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_'8-1',_'name':_'to_help_others_make_decisions'}</t>
+          <t>to_help_others_make_decisions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': '8-1', 'name': 'To help others make decisions'}</t>
+          <t>To help others make decisions</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_'8-2',_'name':_'for_reporting_or_auditing'}</t>
+          <t>for_reporting_or_auditing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': '8-2', 'name': 'For reporting or auditing'}</t>
+          <t>For reporting or auditing</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_'8-3',_'name':_'for_research'}</t>
+          <t>for_research</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': '8-3', 'name': 'For research'}</t>
+          <t>For research</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_'9-1',_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': '9-1', 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_'9-2',_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': '9-2', 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_'10-1',_'name':_'colleagues'}</t>
+          <t>colleagues</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': '10-1', 'name': 'Colleagues'}</t>
+          <t>Colleagues</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_'10-2',_'name':_'management'}</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': '10-2', 'name': 'Management'}</t>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_'10-3',_'name':_'clients'}</t>
+          <t>clients</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': '10-3', 'name': 'Clients'}</t>
+          <t>Clients</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_'10-4',_'name':_'suppliers'}</t>
+          <t>suppliers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': '10-4', 'name': 'Suppliers'}</t>
+          <t>Suppliers</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_'14-1',_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': '14-1', 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_'14-2',_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': '14-2', 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_'14-3',_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': '14-3', 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
